--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:20</t>
+    <t xml:space="preserve">2026-09-10 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:34</t>
+    <t xml:space="preserve">2026-09-12 22:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:46</t>
+    <t xml:space="preserve">2026-09-24 00:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:14</t>
+    <t xml:space="preserve">2026-10-02 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:06</t>
+    <t xml:space="preserve">2026-10-04 10:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:47</t>
+    <t xml:space="preserve">2026-10-05 16:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
